--- a/ClosedXML.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
@@ -401,10 +401,10 @@
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:7">
-      <x:c r="C3" s="0" t="n">
+      <x:c r="C3" s="0">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="n">
+      <x:c r="D3" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E3" s="0">
@@ -418,10 +418,10 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
-      <x:c r="C4" s="0" t="n">
+      <x:c r="C4" s="0">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="n">
+      <x:c r="D4" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E4" s="0">
@@ -460,7 +460,7 @@
       <x:c r="A1" s="0">
         <x:f>'Shifting Formulas'!C3</x:f>
       </x:c>
-      <x:c r="B1" s="0" t="n">
+      <x:c r="B1" s="0">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/ClosedXML.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>Avg:</x:t>
   </x:si>
@@ -390,7 +390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -449,7 +449,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>

--- a/ClosedXML.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
@@ -6,8 +6,8 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Shifting Formulas" sheetId="2" r:id="rId2"/>
-    <x:sheet name="WS2" sheetId="3" r:id="rId3"/>
+    <x:sheet name="Shifting Formulas" sheetId="1" r:id="rId2"/>
+    <x:sheet name="WS2" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="WorksheetB4C4" localSheetId="0">'Shifting Formulas'!$C$5:$D$5</x:definedName>
